--- a/templates/chef-template.xlsx
+++ b/templates/chef-template.xlsx
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">Nutrafi Kitchen Abu Dhabi</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Slot</t>
   </si>
   <si>
     <t xml:space="preserve">Delivery Time</t>
@@ -68,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -104,12 +101,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -188,7 +179,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -198,10 +189,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -296,9 +283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>532800</xdr:colOff>
+      <xdr:colOff>532440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>330480</xdr:rowOff>
+      <xdr:rowOff>330120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -312,7 +299,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="66960" y="36000"/>
-          <a:ext cx="465840" cy="294480"/>
+          <a:ext cx="465480" cy="294120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -333,12 +320,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ6"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="27.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="27.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="29.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="29.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.49"/>
@@ -376,7 +363,7 @@
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -394,11 +381,8 @@
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" s="4" customFormat="true" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="3" customFormat="true" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0"/>
       <c r="B3" s="0"/>
       <c r="C3" s="0"/>
@@ -740,7 +724,7 @@
     </row>
     <row r="4" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F6" s="5"/>
+      <c r="F6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/chef-template.xlsx
+++ b/templates/chef-template.xlsx
@@ -177,7 +177,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -193,7 +193,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -201,7 +201,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -288,9 +288,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>756720</xdr:colOff>
+      <xdr:colOff>756360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>422280</xdr:rowOff>
+      <xdr:rowOff>421920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -304,7 +304,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="144360" y="36000"/>
-          <a:ext cx="612360" cy="386280"/>
+          <a:ext cx="612000" cy="385920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
